--- a/testcases/Automation_Test_Report.xlsx
+++ b/testcases/Automation_Test_Report.xlsx
@@ -629,8 +629,10 @@
           <t>Android Appium Authentication Spec #01</t>
         </is>
       </c>
-      <c r="D2" s="6" t="n">
-        <v>0.06</v>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
@@ -652,8 +654,10 @@
           <t>Android Appium Authentication Spec #02</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n">
-        <v>0.08</v>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -675,8 +679,10 @@
           <t>Android Appium Authentication Spec #03</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n">
-        <v>0.1</v>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
@@ -698,8 +704,10 @@
           <t>Android Appium Authentication Spec #04</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n">
-        <v>0.12</v>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -721,8 +729,10 @@
           <t>Android Appium Authentication Spec #05</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n">
-        <v>0.04</v>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
@@ -744,8 +754,10 @@
           <t>Android Appium Authentication Spec #06</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n">
-        <v>0.06</v>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
@@ -767,8 +779,10 @@
           <t>Android Appium Authentication Spec #07</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n">
-        <v>0.08</v>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
@@ -790,8 +804,10 @@
           <t>Android Appium Authentication Spec #08</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n">
-        <v>0.1</v>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
@@ -813,8 +829,10 @@
           <t>Android Appium Authentication Spec #09</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n">
-        <v>0.12</v>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
@@ -836,8 +854,10 @@
           <t>Android Appium Authentication Spec #10</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n">
-        <v>0.04</v>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
@@ -859,8 +879,10 @@
           <t>Android Appium Authentication Spec #11</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n">
-        <v>0.06</v>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
@@ -882,8 +904,10 @@
           <t>Android Appium Authentication Spec #12</t>
         </is>
       </c>
-      <c r="D13" s="6" t="n">
-        <v>0.08</v>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
@@ -905,8 +929,10 @@
           <t>Android Appium Authentication Spec #13</t>
         </is>
       </c>
-      <c r="D14" s="6" t="n">
-        <v>0.1</v>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
@@ -928,8 +954,10 @@
           <t>Android Appium Authentication Spec #14</t>
         </is>
       </c>
-      <c r="D15" s="6" t="n">
-        <v>0.12</v>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -951,8 +979,10 @@
           <t>Android Appium Authentication Spec #15</t>
         </is>
       </c>
-      <c r="D16" s="6" t="n">
-        <v>0.04</v>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
@@ -974,8 +1004,10 @@
           <t>Android Appium Authentication Spec #16</t>
         </is>
       </c>
-      <c r="D17" s="6" t="n">
-        <v>0.06</v>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
@@ -997,8 +1029,10 @@
           <t>Android Appium Authentication Spec #17</t>
         </is>
       </c>
-      <c r="D18" s="6" t="n">
-        <v>0.08</v>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
@@ -1020,8 +1054,10 @@
           <t>Android Appium Authentication Spec #18</t>
         </is>
       </c>
-      <c r="D19" s="6" t="n">
-        <v>0.1</v>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
@@ -1043,8 +1079,10 @@
           <t>Android Appium Authentication Spec #19</t>
         </is>
       </c>
-      <c r="D20" s="6" t="n">
-        <v>0.12</v>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
@@ -1066,8 +1104,10 @@
           <t>Android Appium Authentication Spec #20</t>
         </is>
       </c>
-      <c r="D21" s="6" t="n">
-        <v>0.04</v>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
@@ -1089,8 +1129,10 @@
           <t>Android Appium Authentication Spec #21</t>
         </is>
       </c>
-      <c r="D22" s="6" t="n">
-        <v>0.06</v>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -1112,8 +1154,10 @@
           <t>Android Appium Authentication Spec #22</t>
         </is>
       </c>
-      <c r="D23" s="6" t="n">
-        <v>0.08</v>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
@@ -1135,8 +1179,10 @@
           <t>Android Appium Authentication Spec #23</t>
         </is>
       </c>
-      <c r="D24" s="6" t="n">
-        <v>0.1</v>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
@@ -1158,8 +1204,10 @@
           <t>Android Appium Authentication Spec #24</t>
         </is>
       </c>
-      <c r="D25" s="6" t="n">
-        <v>0.12</v>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
@@ -1181,8 +1229,10 @@
           <t>Android Appium Authentication Spec #25</t>
         </is>
       </c>
-      <c r="D26" s="6" t="n">
-        <v>0.04</v>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
@@ -1204,8 +1254,10 @@
           <t>Android Appium Authentication Spec #26</t>
         </is>
       </c>
-      <c r="D27" s="6" t="n">
-        <v>0.06</v>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
@@ -1227,8 +1279,10 @@
           <t>Android Appium Authentication Spec #27</t>
         </is>
       </c>
-      <c r="D28" s="6" t="n">
-        <v>0.08</v>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
@@ -1250,8 +1304,10 @@
           <t>Android Appium Authentication Spec #28</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n">
-        <v>0.1</v>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
@@ -1273,8 +1329,10 @@
           <t>Android Appium Authentication Spec #29</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n">
-        <v>0.12</v>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
@@ -1296,8 +1354,10 @@
           <t>Android Appium Authentication Spec #30</t>
         </is>
       </c>
-      <c r="D31" s="6" t="n">
-        <v>0.04</v>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
@@ -1319,8 +1379,10 @@
           <t>Android Appium Authentication Spec #31</t>
         </is>
       </c>
-      <c r="D32" s="6" t="n">
-        <v>0.06</v>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
@@ -1342,8 +1404,10 @@
           <t>Android Appium Authentication Spec #32</t>
         </is>
       </c>
-      <c r="D33" s="6" t="n">
-        <v>0.08</v>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
@@ -1365,8 +1429,10 @@
           <t>Android Appium Authentication Spec #33</t>
         </is>
       </c>
-      <c r="D34" s="6" t="n">
-        <v>0.1</v>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
@@ -1388,8 +1454,10 @@
           <t>Android Appium Authentication Spec #34</t>
         </is>
       </c>
-      <c r="D35" s="6" t="n">
-        <v>0.12</v>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -1411,8 +1479,10 @@
           <t>Android Appium Authentication Spec #35</t>
         </is>
       </c>
-      <c r="D36" s="6" t="n">
-        <v>0.04</v>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
@@ -1434,8 +1504,10 @@
           <t>Android Appium Authentication Spec #36</t>
         </is>
       </c>
-      <c r="D37" s="6" t="n">
-        <v>0.06</v>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
@@ -1457,8 +1529,10 @@
           <t>Android Appium Authentication Spec #37</t>
         </is>
       </c>
-      <c r="D38" s="6" t="n">
-        <v>0.08</v>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
@@ -1480,8 +1554,10 @@
           <t>Android Appium Authentication Spec #38</t>
         </is>
       </c>
-      <c r="D39" s="6" t="n">
-        <v>0.1</v>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
@@ -1503,8 +1579,10 @@
           <t>Android Appium Authentication Spec #39</t>
         </is>
       </c>
-      <c r="D40" s="6" t="n">
-        <v>0.12</v>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
@@ -1526,8 +1604,10 @@
           <t>Android Appium Authentication Spec #40</t>
         </is>
       </c>
-      <c r="D41" s="6" t="n">
-        <v>0.04</v>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
@@ -1549,8 +1629,10 @@
           <t>Android Appium Authorization Spec #01</t>
         </is>
       </c>
-      <c r="D42" s="6" t="n">
-        <v>0.06</v>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
@@ -1572,8 +1654,10 @@
           <t>Android Appium Authorization Spec #02</t>
         </is>
       </c>
-      <c r="D43" s="6" t="n">
-        <v>0.08</v>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
@@ -1595,8 +1679,10 @@
           <t>Android Appium Authorization Spec #03</t>
         </is>
       </c>
-      <c r="D44" s="6" t="n">
-        <v>0.1</v>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
@@ -1618,8 +1704,10 @@
           <t>Android Appium Authorization Spec #04</t>
         </is>
       </c>
-      <c r="D45" s="6" t="n">
-        <v>0.12</v>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
@@ -1641,8 +1729,10 @@
           <t>Android Appium Authorization Spec #05</t>
         </is>
       </c>
-      <c r="D46" s="6" t="n">
-        <v>0.04</v>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
@@ -1664,8 +1754,10 @@
           <t>Android Appium Authorization Spec #06</t>
         </is>
       </c>
-      <c r="D47" s="6" t="n">
-        <v>0.06</v>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -1687,8 +1779,10 @@
           <t>Android Appium Authorization Spec #07</t>
         </is>
       </c>
-      <c r="D48" s="6" t="n">
-        <v>0.08</v>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
@@ -1710,8 +1804,10 @@
           <t>Android Appium Authorization Spec #08</t>
         </is>
       </c>
-      <c r="D49" s="6" t="n">
-        <v>0.1</v>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
@@ -1733,8 +1829,10 @@
           <t>Android Appium Authorization Spec #09</t>
         </is>
       </c>
-      <c r="D50" s="6" t="n">
-        <v>0.12</v>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
@@ -1756,8 +1854,10 @@
           <t>Android Appium Authorization Spec #10</t>
         </is>
       </c>
-      <c r="D51" s="6" t="n">
-        <v>0.04</v>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
@@ -1779,8 +1879,10 @@
           <t>Android Appium Authorization Spec #11</t>
         </is>
       </c>
-      <c r="D52" s="6" t="n">
-        <v>0.06</v>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
@@ -1802,8 +1904,10 @@
           <t>Android Appium Authorization Spec #12</t>
         </is>
       </c>
-      <c r="D53" s="6" t="n">
-        <v>0.08</v>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
@@ -1825,8 +1929,10 @@
           <t>Android Appium Authorization Spec #13</t>
         </is>
       </c>
-      <c r="D54" s="6" t="n">
-        <v>0.1</v>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
@@ -1848,8 +1954,10 @@
           <t>Android Appium Authorization Spec #14</t>
         </is>
       </c>
-      <c r="D55" s="6" t="n">
-        <v>0.12</v>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
@@ -1871,8 +1979,10 @@
           <t>Android Appium Authorization Spec #15</t>
         </is>
       </c>
-      <c r="D56" s="6" t="n">
-        <v>0.04</v>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
@@ -1894,8 +2004,10 @@
           <t>Android Appium Authorization Spec #16</t>
         </is>
       </c>
-      <c r="D57" s="6" t="n">
-        <v>0.06</v>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
@@ -1917,8 +2029,10 @@
           <t>Android Appium Authorization Spec #17</t>
         </is>
       </c>
-      <c r="D58" s="6" t="n">
-        <v>0.08</v>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
@@ -1940,8 +2054,10 @@
           <t>Android Appium Authorization Spec #18</t>
         </is>
       </c>
-      <c r="D59" s="6" t="n">
-        <v>0.1</v>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
@@ -1963,8 +2079,10 @@
           <t>Android Appium Authorization Spec #19</t>
         </is>
       </c>
-      <c r="D60" s="6" t="n">
-        <v>0.12</v>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
@@ -1986,8 +2104,10 @@
           <t>Android Appium Authorization Spec #20</t>
         </is>
       </c>
-      <c r="D61" s="6" t="n">
-        <v>0.04</v>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
@@ -2009,8 +2129,10 @@
           <t>Android Appium Authorization Spec #21</t>
         </is>
       </c>
-      <c r="D62" s="6" t="n">
-        <v>0.06</v>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -2032,8 +2154,10 @@
           <t>Android Appium Authorization Spec #22</t>
         </is>
       </c>
-      <c r="D63" s="6" t="n">
-        <v>0.08</v>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
@@ -2055,8 +2179,10 @@
           <t>Android Appium Authorization Spec #23</t>
         </is>
       </c>
-      <c r="D64" s="6" t="n">
-        <v>0.1</v>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
@@ -2078,8 +2204,10 @@
           <t>Android Appium Authorization Spec #24</t>
         </is>
       </c>
-      <c r="D65" s="6" t="n">
-        <v>0.12</v>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
@@ -2101,8 +2229,10 @@
           <t>Android Appium Authorization Spec #25</t>
         </is>
       </c>
-      <c r="D66" s="6" t="n">
-        <v>0.04</v>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
@@ -2124,8 +2254,10 @@
           <t>Android Appium Authorization Spec #26</t>
         </is>
       </c>
-      <c r="D67" s="6" t="n">
-        <v>0.06</v>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
@@ -2147,8 +2279,10 @@
           <t>Android Appium Authorization Spec #27</t>
         </is>
       </c>
-      <c r="D68" s="6" t="n">
-        <v>0.08</v>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
@@ -2170,8 +2304,10 @@
           <t>Android Appium Authorization Spec #28</t>
         </is>
       </c>
-      <c r="D69" s="6" t="n">
-        <v>0.1</v>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
@@ -2193,8 +2329,10 @@
           <t>Android Appium Authorization Spec #29</t>
         </is>
       </c>
-      <c r="D70" s="6" t="n">
-        <v>0.12</v>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
@@ -2216,8 +2354,10 @@
           <t>Android Appium Authorization Spec #30</t>
         </is>
       </c>
-      <c r="D71" s="6" t="n">
-        <v>0.04</v>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
@@ -2239,8 +2379,10 @@
           <t>Android Appium Registration Spec #01</t>
         </is>
       </c>
-      <c r="D72" s="6" t="n">
-        <v>0.06</v>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
@@ -2262,8 +2404,10 @@
           <t>Android Appium Registration Spec #02</t>
         </is>
       </c>
-      <c r="D73" s="6" t="n">
-        <v>0.08</v>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
@@ -2285,8 +2429,10 @@
           <t>Android Appium Registration Spec #03</t>
         </is>
       </c>
-      <c r="D74" s="6" t="n">
-        <v>0.1</v>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
@@ -2308,8 +2454,10 @@
           <t>Android Appium Registration Spec #04</t>
         </is>
       </c>
-      <c r="D75" s="6" t="n">
-        <v>0.12</v>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
@@ -2331,8 +2479,10 @@
           <t>Android Appium Registration Spec #05</t>
         </is>
       </c>
-      <c r="D76" s="6" t="n">
-        <v>0.04</v>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
@@ -2354,8 +2504,10 @@
           <t>Android Appium Registration Spec #06</t>
         </is>
       </c>
-      <c r="D77" s="6" t="n">
-        <v>0.06</v>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
@@ -2377,8 +2529,10 @@
           <t>Android Appium Registration Spec #07</t>
         </is>
       </c>
-      <c r="D78" s="6" t="n">
-        <v>0.08</v>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
@@ -2400,8 +2554,10 @@
           <t>Android Appium Registration Spec #08</t>
         </is>
       </c>
-      <c r="D79" s="6" t="n">
-        <v>0.1</v>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
@@ -2423,8 +2579,10 @@
           <t>Android Appium Registration Spec #09</t>
         </is>
       </c>
-      <c r="D80" s="6" t="n">
-        <v>0.12</v>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
@@ -2446,8 +2604,10 @@
           <t>Android Appium Registration Spec #10</t>
         </is>
       </c>
-      <c r="D81" s="6" t="n">
-        <v>0.04</v>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
@@ -2469,8 +2629,10 @@
           <t>Android Appium Registration Spec #11</t>
         </is>
       </c>
-      <c r="D82" s="6" t="n">
-        <v>0.06</v>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
@@ -2492,8 +2654,10 @@
           <t>Android Appium Registration Spec #12</t>
         </is>
       </c>
-      <c r="D83" s="6" t="n">
-        <v>0.08</v>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
@@ -2515,8 +2679,10 @@
           <t>Android Appium Registration Spec #13</t>
         </is>
       </c>
-      <c r="D84" s="6" t="n">
-        <v>0.1</v>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
@@ -2538,8 +2704,10 @@
           <t>Android Appium Registration Spec #14</t>
         </is>
       </c>
-      <c r="D85" s="6" t="n">
-        <v>0.12</v>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
@@ -2561,8 +2729,10 @@
           <t>Android Appium Registration Spec #15</t>
         </is>
       </c>
-      <c r="D86" s="6" t="n">
-        <v>0.04</v>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
@@ -2584,8 +2754,10 @@
           <t>Android Appium Registration Spec #16</t>
         </is>
       </c>
-      <c r="D87" s="6" t="n">
-        <v>0.06</v>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
@@ -2607,8 +2779,10 @@
           <t>Android Appium Registration Spec #17</t>
         </is>
       </c>
-      <c r="D88" s="6" t="n">
-        <v>0.08</v>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
@@ -2630,8 +2804,10 @@
           <t>Android Appium Registration Spec #18</t>
         </is>
       </c>
-      <c r="D89" s="6" t="n">
-        <v>0.1</v>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
@@ -2653,8 +2829,10 @@
           <t>Android Appium Registration Spec #19</t>
         </is>
       </c>
-      <c r="D90" s="6" t="n">
-        <v>0.12</v>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
@@ -2676,8 +2854,10 @@
           <t>Android Appium Registration Spec #20</t>
         </is>
       </c>
-      <c r="D91" s="6" t="n">
-        <v>0.04</v>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
@@ -2699,8 +2879,10 @@
           <t>Android Appium Profile Management Spec #01</t>
         </is>
       </c>
-      <c r="D92" s="6" t="n">
-        <v>0.06</v>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
@@ -2722,8 +2904,10 @@
           <t>Android Appium Profile Management Spec #02</t>
         </is>
       </c>
-      <c r="D93" s="6" t="n">
-        <v>0.08</v>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
@@ -2745,8 +2929,10 @@
           <t>Android Appium Profile Management Spec #03</t>
         </is>
       </c>
-      <c r="D94" s="6" t="n">
-        <v>0.1</v>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
@@ -2768,8 +2954,10 @@
           <t>Android Appium Profile Management Spec #04</t>
         </is>
       </c>
-      <c r="D95" s="6" t="n">
-        <v>0.12</v>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
@@ -2791,8 +2979,10 @@
           <t>Android Appium Profile Management Spec #05</t>
         </is>
       </c>
-      <c r="D96" s="6" t="n">
-        <v>0.04</v>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
@@ -2814,8 +3004,10 @@
           <t>Android Appium Profile Management Spec #06</t>
         </is>
       </c>
-      <c r="D97" s="6" t="n">
-        <v>0.06</v>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
@@ -2837,8 +3029,10 @@
           <t>Android Appium Profile Management Spec #07</t>
         </is>
       </c>
-      <c r="D98" s="6" t="n">
-        <v>0.08</v>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
@@ -2860,8 +3054,10 @@
           <t>Android Appium Profile Management Spec #08</t>
         </is>
       </c>
-      <c r="D99" s="6" t="n">
-        <v>0.1</v>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
@@ -2883,8 +3079,10 @@
           <t>Android Appium Profile Management Spec #09</t>
         </is>
       </c>
-      <c r="D100" s="6" t="n">
-        <v>0.12</v>
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
@@ -2906,8 +3104,10 @@
           <t>Android Appium Profile Management Spec #10</t>
         </is>
       </c>
-      <c r="D101" s="6" t="n">
-        <v>0.04</v>
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
@@ -2929,8 +3129,10 @@
           <t>Android Appium Profile Management Spec #11</t>
         </is>
       </c>
-      <c r="D102" s="6" t="n">
-        <v>0.06</v>
+      <c r="D102" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
@@ -2952,8 +3154,10 @@
           <t>Android Appium Profile Management Spec #12</t>
         </is>
       </c>
-      <c r="D103" s="6" t="n">
-        <v>0.08</v>
+      <c r="D103" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
@@ -2975,8 +3179,10 @@
           <t>Android Appium Profile Management Spec #13</t>
         </is>
       </c>
-      <c r="D104" s="6" t="n">
-        <v>0.1</v>
+      <c r="D104" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
@@ -2998,8 +3204,10 @@
           <t>Android Appium Profile Management Spec #14</t>
         </is>
       </c>
-      <c r="D105" s="6" t="n">
-        <v>0.12</v>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
@@ -3021,8 +3229,10 @@
           <t>Android Appium Profile Management Spec #15</t>
         </is>
       </c>
-      <c r="D106" s="6" t="n">
-        <v>0.04</v>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
@@ -3044,8 +3254,10 @@
           <t>Android Appium Profile Management Spec #16</t>
         </is>
       </c>
-      <c r="D107" s="6" t="n">
-        <v>0.06</v>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
@@ -3067,8 +3279,10 @@
           <t>Android Appium Profile Management Spec #17</t>
         </is>
       </c>
-      <c r="D108" s="6" t="n">
-        <v>0.08</v>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
@@ -3090,8 +3304,10 @@
           <t>Android Appium Profile Management Spec #18</t>
         </is>
       </c>
-      <c r="D109" s="6" t="n">
-        <v>0.1</v>
+      <c r="D109" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
@@ -3113,8 +3329,10 @@
           <t>Android Appium Profile Management Spec #19</t>
         </is>
       </c>
-      <c r="D110" s="6" t="n">
-        <v>0.12</v>
+      <c r="D110" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
@@ -3136,8 +3354,10 @@
           <t>Android Appium Profile Management Spec #20</t>
         </is>
       </c>
-      <c r="D111" s="6" t="n">
-        <v>0.04</v>
+      <c r="D111" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
@@ -3159,8 +3379,10 @@
           <t>Android Appium Navigation Spec #01</t>
         </is>
       </c>
-      <c r="D112" s="6" t="n">
-        <v>0.06</v>
+      <c r="D112" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
@@ -3182,8 +3404,10 @@
           <t>Android Appium Navigation Spec #02</t>
         </is>
       </c>
-      <c r="D113" s="6" t="n">
-        <v>0.08</v>
+      <c r="D113" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
@@ -3205,8 +3429,10 @@
           <t>Android Appium Navigation Spec #03</t>
         </is>
       </c>
-      <c r="D114" s="6" t="n">
-        <v>0.1</v>
+      <c r="D114" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
@@ -3228,8 +3454,10 @@
           <t>Android Appium Navigation Spec #04</t>
         </is>
       </c>
-      <c r="D115" s="6" t="n">
-        <v>0.12</v>
+      <c r="D115" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
@@ -3251,8 +3479,10 @@
           <t>Android Appium Navigation Spec #05</t>
         </is>
       </c>
-      <c r="D116" s="6" t="n">
-        <v>0.04</v>
+      <c r="D116" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
@@ -3274,8 +3504,10 @@
           <t>Android Appium Navigation Spec #06</t>
         </is>
       </c>
-      <c r="D117" s="6" t="n">
-        <v>0.06</v>
+      <c r="D117" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
@@ -3297,8 +3529,10 @@
           <t>Android Appium Navigation Spec #07</t>
         </is>
       </c>
-      <c r="D118" s="6" t="n">
-        <v>0.08</v>
+      <c r="D118" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
@@ -3320,8 +3554,10 @@
           <t>Android Appium Navigation Spec #08</t>
         </is>
       </c>
-      <c r="D119" s="6" t="n">
-        <v>0.1</v>
+      <c r="D119" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
@@ -3343,8 +3579,10 @@
           <t>Android Appium Navigation Spec #09</t>
         </is>
       </c>
-      <c r="D120" s="6" t="n">
-        <v>0.12</v>
+      <c r="D120" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
@@ -3366,8 +3604,10 @@
           <t>Android Appium Navigation Spec #10</t>
         </is>
       </c>
-      <c r="D121" s="6" t="n">
-        <v>0.04</v>
+      <c r="D121" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
@@ -3389,8 +3629,10 @@
           <t>Android Appium Navigation Spec #11</t>
         </is>
       </c>
-      <c r="D122" s="6" t="n">
-        <v>0.06</v>
+      <c r="D122" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
@@ -3412,8 +3654,10 @@
           <t>Android Appium Navigation Spec #12</t>
         </is>
       </c>
-      <c r="D123" s="6" t="n">
-        <v>0.08</v>
+      <c r="D123" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
@@ -3435,8 +3679,10 @@
           <t>Android Appium Navigation Spec #13</t>
         </is>
       </c>
-      <c r="D124" s="6" t="n">
-        <v>0.1</v>
+      <c r="D124" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
@@ -3458,8 +3704,10 @@
           <t>Android Appium Navigation Spec #14</t>
         </is>
       </c>
-      <c r="D125" s="6" t="n">
-        <v>0.12</v>
+      <c r="D125" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
@@ -3481,8 +3729,10 @@
           <t>Android Appium Navigation Spec #15</t>
         </is>
       </c>
-      <c r="D126" s="6" t="n">
-        <v>0.04</v>
+      <c r="D126" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
@@ -3504,8 +3754,10 @@
           <t>Android Appium Navigation Spec #16</t>
         </is>
       </c>
-      <c r="D127" s="6" t="n">
-        <v>0.06</v>
+      <c r="D127" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
@@ -3527,8 +3779,10 @@
           <t>Android Appium Navigation Spec #17</t>
         </is>
       </c>
-      <c r="D128" s="6" t="n">
-        <v>0.08</v>
+      <c r="D128" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
@@ -3550,8 +3804,10 @@
           <t>Android Appium Navigation Spec #18</t>
         </is>
       </c>
-      <c r="D129" s="6" t="n">
-        <v>0.1</v>
+      <c r="D129" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
@@ -3573,8 +3829,10 @@
           <t>Android Appium Navigation Spec #19</t>
         </is>
       </c>
-      <c r="D130" s="6" t="n">
-        <v>0.12</v>
+      <c r="D130" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
@@ -3596,8 +3854,10 @@
           <t>Android Appium Navigation Spec #20</t>
         </is>
       </c>
-      <c r="D131" s="6" t="n">
-        <v>0.04</v>
+      <c r="D131" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
@@ -3619,8 +3879,10 @@
           <t>Android Appium Navigation Spec #21</t>
         </is>
       </c>
-      <c r="D132" s="6" t="n">
-        <v>0.06</v>
+      <c r="D132" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
@@ -3642,8 +3904,10 @@
           <t>Android Appium Navigation Spec #22</t>
         </is>
       </c>
-      <c r="D133" s="6" t="n">
-        <v>0.08</v>
+      <c r="D133" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
@@ -3665,8 +3929,10 @@
           <t>Android Appium Navigation Spec #23</t>
         </is>
       </c>
-      <c r="D134" s="6" t="n">
-        <v>0.1</v>
+      <c r="D134" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
@@ -3688,8 +3954,10 @@
           <t>Android Appium Navigation Spec #24</t>
         </is>
       </c>
-      <c r="D135" s="6" t="n">
-        <v>0.12</v>
+      <c r="D135" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
@@ -3711,8 +3979,10 @@
           <t>Android Appium Navigation Spec #25</t>
         </is>
       </c>
-      <c r="D136" s="6" t="n">
-        <v>0.04</v>
+      <c r="D136" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
@@ -3734,8 +4004,10 @@
           <t>Android Appium Navigation Spec #26</t>
         </is>
       </c>
-      <c r="D137" s="6" t="n">
-        <v>0.06</v>
+      <c r="D137" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
@@ -3757,8 +4029,10 @@
           <t>Android Appium Navigation Spec #27</t>
         </is>
       </c>
-      <c r="D138" s="6" t="n">
-        <v>0.08</v>
+      <c r="D138" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
@@ -3780,8 +4054,10 @@
           <t>Android Appium Navigation Spec #28</t>
         </is>
       </c>
-      <c r="D139" s="6" t="n">
-        <v>0.1</v>
+      <c r="D139" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
@@ -3803,8 +4079,10 @@
           <t>Android Appium Navigation Spec #29</t>
         </is>
       </c>
-      <c r="D140" s="6" t="n">
-        <v>0.12</v>
+      <c r="D140" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E140" s="4" t="inlineStr">
         <is>
@@ -3826,8 +4104,10 @@
           <t>Android Appium Navigation Spec #30</t>
         </is>
       </c>
-      <c r="D141" s="6" t="n">
-        <v>0.04</v>
+      <c r="D141" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
@@ -3849,8 +4129,10 @@
           <t>Android Appium Dashboard Spec #01</t>
         </is>
       </c>
-      <c r="D142" s="6" t="n">
-        <v>0.06</v>
+      <c r="D142" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E142" s="4" t="inlineStr">
         <is>
@@ -3872,8 +4154,10 @@
           <t>Android Appium Dashboard Spec #02</t>
         </is>
       </c>
-      <c r="D143" s="6" t="n">
-        <v>0.08</v>
+      <c r="D143" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
@@ -3895,8 +4179,10 @@
           <t>Android Appium Dashboard Spec #03</t>
         </is>
       </c>
-      <c r="D144" s="6" t="n">
-        <v>0.1</v>
+      <c r="D144" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E144" s="4" t="inlineStr">
         <is>
@@ -3918,8 +4204,10 @@
           <t>Android Appium Dashboard Spec #04</t>
         </is>
       </c>
-      <c r="D145" s="6" t="n">
-        <v>0.12</v>
+      <c r="D145" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
@@ -3941,8 +4229,10 @@
           <t>Android Appium Dashboard Spec #05</t>
         </is>
       </c>
-      <c r="D146" s="6" t="n">
-        <v>0.04</v>
+      <c r="D146" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E146" s="4" t="inlineStr">
         <is>
@@ -3964,8 +4254,10 @@
           <t>Android Appium Dashboard Spec #06</t>
         </is>
       </c>
-      <c r="D147" s="6" t="n">
-        <v>0.06</v>
+      <c r="D147" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E147" s="4" t="inlineStr">
         <is>
@@ -3987,8 +4279,10 @@
           <t>Android Appium Dashboard Spec #07</t>
         </is>
       </c>
-      <c r="D148" s="6" t="n">
-        <v>0.08</v>
+      <c r="D148" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E148" s="4" t="inlineStr">
         <is>
@@ -4010,8 +4304,10 @@
           <t>Android Appium Dashboard Spec #08</t>
         </is>
       </c>
-      <c r="D149" s="6" t="n">
-        <v>0.1</v>
+      <c r="D149" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
@@ -4033,8 +4329,10 @@
           <t>Android Appium Dashboard Spec #09</t>
         </is>
       </c>
-      <c r="D150" s="6" t="n">
-        <v>0.12</v>
+      <c r="D150" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E150" s="4" t="inlineStr">
         <is>
@@ -4056,8 +4354,10 @@
           <t>Android Appium Dashboard Spec #10</t>
         </is>
       </c>
-      <c r="D151" s="6" t="n">
-        <v>0.04</v>
+      <c r="D151" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E151" s="4" t="inlineStr">
         <is>
@@ -4079,8 +4379,10 @@
           <t>Android Appium Dashboard Spec #11</t>
         </is>
       </c>
-      <c r="D152" s="6" t="n">
-        <v>0.06</v>
+      <c r="D152" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E152" s="4" t="inlineStr">
         <is>
@@ -4102,8 +4404,10 @@
           <t>Android Appium Dashboard Spec #12</t>
         </is>
       </c>
-      <c r="D153" s="6" t="n">
-        <v>0.08</v>
+      <c r="D153" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E153" s="4" t="inlineStr">
         <is>
@@ -4125,8 +4429,10 @@
           <t>Android Appium Dashboard Spec #13</t>
         </is>
       </c>
-      <c r="D154" s="6" t="n">
-        <v>0.1</v>
+      <c r="D154" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E154" s="4" t="inlineStr">
         <is>
@@ -4148,8 +4454,10 @@
           <t>Android Appium Dashboard Spec #14</t>
         </is>
       </c>
-      <c r="D155" s="6" t="n">
-        <v>0.12</v>
+      <c r="D155" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E155" s="4" t="inlineStr">
         <is>
@@ -4171,8 +4479,10 @@
           <t>Android Appium Dashboard Spec #15</t>
         </is>
       </c>
-      <c r="D156" s="6" t="n">
-        <v>0.04</v>
+      <c r="D156" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E156" s="4" t="inlineStr">
         <is>
@@ -4194,8 +4504,10 @@
           <t>Android Appium Dashboard Spec #16</t>
         </is>
       </c>
-      <c r="D157" s="6" t="n">
-        <v>0.06</v>
+      <c r="D157" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E157" s="4" t="inlineStr">
         <is>
@@ -4217,8 +4529,10 @@
           <t>Android Appium Dashboard Spec #17</t>
         </is>
       </c>
-      <c r="D158" s="6" t="n">
-        <v>0.08</v>
+      <c r="D158" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E158" s="4" t="inlineStr">
         <is>
@@ -4240,8 +4554,10 @@
           <t>Android Appium Dashboard Spec #18</t>
         </is>
       </c>
-      <c r="D159" s="6" t="n">
-        <v>0.1</v>
+      <c r="D159" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E159" s="4" t="inlineStr">
         <is>
@@ -4263,8 +4579,10 @@
           <t>Android Appium Dashboard Spec #19</t>
         </is>
       </c>
-      <c r="D160" s="6" t="n">
-        <v>0.12</v>
+      <c r="D160" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E160" s="4" t="inlineStr">
         <is>
@@ -4286,8 +4604,10 @@
           <t>Android Appium Dashboard Spec #20</t>
         </is>
       </c>
-      <c r="D161" s="6" t="n">
-        <v>0.04</v>
+      <c r="D161" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E161" s="4" t="inlineStr">
         <is>
@@ -4309,8 +4629,10 @@
           <t>Android Appium Forms Spec #01</t>
         </is>
       </c>
-      <c r="D162" s="6" t="n">
-        <v>0.06</v>
+      <c r="D162" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E162" s="4" t="inlineStr">
         <is>
@@ -4332,8 +4654,10 @@
           <t>Android Appium Forms Spec #02</t>
         </is>
       </c>
-      <c r="D163" s="6" t="n">
-        <v>0.08</v>
+      <c r="D163" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E163" s="4" t="inlineStr">
         <is>
@@ -4355,8 +4679,10 @@
           <t>Android Appium Forms Spec #03</t>
         </is>
       </c>
-      <c r="D164" s="6" t="n">
-        <v>0.1</v>
+      <c r="D164" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E164" s="4" t="inlineStr">
         <is>
@@ -4378,8 +4704,10 @@
           <t>Android Appium Forms Spec #04</t>
         </is>
       </c>
-      <c r="D165" s="6" t="n">
-        <v>0.12</v>
+      <c r="D165" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E165" s="4" t="inlineStr">
         <is>
@@ -4401,8 +4729,10 @@
           <t>Android Appium Forms Spec #05</t>
         </is>
       </c>
-      <c r="D166" s="6" t="n">
-        <v>0.04</v>
+      <c r="D166" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E166" s="4" t="inlineStr">
         <is>
@@ -4424,8 +4754,10 @@
           <t>Android Appium Forms Spec #06</t>
         </is>
       </c>
-      <c r="D167" s="6" t="n">
-        <v>0.06</v>
+      <c r="D167" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E167" s="4" t="inlineStr">
         <is>
@@ -4447,8 +4779,10 @@
           <t>Android Appium Forms Spec #07</t>
         </is>
       </c>
-      <c r="D168" s="6" t="n">
-        <v>0.08</v>
+      <c r="D168" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E168" s="4" t="inlineStr">
         <is>
@@ -4470,8 +4804,10 @@
           <t>Android Appium Forms Spec #08</t>
         </is>
       </c>
-      <c r="D169" s="6" t="n">
-        <v>0.1</v>
+      <c r="D169" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E169" s="4" t="inlineStr">
         <is>
@@ -4493,8 +4829,10 @@
           <t>Android Appium Forms Spec #09</t>
         </is>
       </c>
-      <c r="D170" s="6" t="n">
-        <v>0.12</v>
+      <c r="D170" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E170" s="4" t="inlineStr">
         <is>
@@ -4516,8 +4854,10 @@
           <t>Android Appium Forms Spec #10</t>
         </is>
       </c>
-      <c r="D171" s="6" t="n">
-        <v>0.04</v>
+      <c r="D171" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E171" s="4" t="inlineStr">
         <is>
@@ -4539,8 +4879,10 @@
           <t>Android Appium Forms Spec #11</t>
         </is>
       </c>
-      <c r="D172" s="6" t="n">
-        <v>0.06</v>
+      <c r="D172" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E172" s="4" t="inlineStr">
         <is>
@@ -4562,8 +4904,10 @@
           <t>Android Appium Forms Spec #12</t>
         </is>
       </c>
-      <c r="D173" s="6" t="n">
-        <v>0.08</v>
+      <c r="D173" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E173" s="4" t="inlineStr">
         <is>
@@ -4585,8 +4929,10 @@
           <t>Android Appium Forms Spec #13</t>
         </is>
       </c>
-      <c r="D174" s="6" t="n">
-        <v>0.1</v>
+      <c r="D174" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E174" s="4" t="inlineStr">
         <is>
@@ -4608,8 +4954,10 @@
           <t>Android Appium Forms Spec #14</t>
         </is>
       </c>
-      <c r="D175" s="6" t="n">
-        <v>0.12</v>
+      <c r="D175" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E175" s="4" t="inlineStr">
         <is>
@@ -4631,8 +4979,10 @@
           <t>Android Appium Forms Spec #15</t>
         </is>
       </c>
-      <c r="D176" s="6" t="n">
-        <v>0.04</v>
+      <c r="D176" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E176" s="4" t="inlineStr">
         <is>
@@ -4654,8 +5004,10 @@
           <t>Android Appium Forms Spec #16</t>
         </is>
       </c>
-      <c r="D177" s="6" t="n">
-        <v>0.06</v>
+      <c r="D177" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E177" s="4" t="inlineStr">
         <is>
@@ -4677,8 +5029,10 @@
           <t>Android Appium Forms Spec #17</t>
         </is>
       </c>
-      <c r="D178" s="6" t="n">
-        <v>0.08</v>
+      <c r="D178" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E178" s="4" t="inlineStr">
         <is>
@@ -4700,8 +5054,10 @@
           <t>Android Appium Forms Spec #18</t>
         </is>
       </c>
-      <c r="D179" s="6" t="n">
-        <v>0.1</v>
+      <c r="D179" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E179" s="4" t="inlineStr">
         <is>
@@ -4723,8 +5079,10 @@
           <t>Android Appium Forms Spec #19</t>
         </is>
       </c>
-      <c r="D180" s="6" t="n">
-        <v>0.12</v>
+      <c r="D180" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E180" s="4" t="inlineStr">
         <is>
@@ -4746,8 +5104,10 @@
           <t>Android Appium Forms Spec #20</t>
         </is>
       </c>
-      <c r="D181" s="6" t="n">
-        <v>0.04</v>
+      <c r="D181" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E181" s="4" t="inlineStr">
         <is>
@@ -4769,8 +5129,10 @@
           <t>Android Appium Forms Spec #21</t>
         </is>
       </c>
-      <c r="D182" s="6" t="n">
-        <v>0.06</v>
+      <c r="D182" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E182" s="4" t="inlineStr">
         <is>
@@ -4792,8 +5154,10 @@
           <t>Android Appium Forms Spec #22</t>
         </is>
       </c>
-      <c r="D183" s="6" t="n">
-        <v>0.08</v>
+      <c r="D183" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E183" s="4" t="inlineStr">
         <is>
@@ -4815,8 +5179,10 @@
           <t>Android Appium Forms Spec #23</t>
         </is>
       </c>
-      <c r="D184" s="6" t="n">
-        <v>0.1</v>
+      <c r="D184" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E184" s="4" t="inlineStr">
         <is>
@@ -4838,8 +5204,10 @@
           <t>Android Appium Forms Spec #24</t>
         </is>
       </c>
-      <c r="D185" s="6" t="n">
-        <v>0.12</v>
+      <c r="D185" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E185" s="4" t="inlineStr">
         <is>
@@ -4861,8 +5229,10 @@
           <t>Android Appium Forms Spec #25</t>
         </is>
       </c>
-      <c r="D186" s="6" t="n">
-        <v>0.04</v>
+      <c r="D186" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E186" s="4" t="inlineStr">
         <is>
@@ -4884,8 +5254,10 @@
           <t>Android Appium Forms Spec #26</t>
         </is>
       </c>
-      <c r="D187" s="6" t="n">
-        <v>0.06</v>
+      <c r="D187" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E187" s="4" t="inlineStr">
         <is>
@@ -4907,8 +5279,10 @@
           <t>Android Appium Forms Spec #27</t>
         </is>
       </c>
-      <c r="D188" s="6" t="n">
-        <v>0.08</v>
+      <c r="D188" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E188" s="4" t="inlineStr">
         <is>
@@ -4930,8 +5304,10 @@
           <t>Android Appium Forms Spec #28</t>
         </is>
       </c>
-      <c r="D189" s="6" t="n">
-        <v>0.1</v>
+      <c r="D189" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E189" s="4" t="inlineStr">
         <is>
@@ -4953,8 +5329,10 @@
           <t>Android Appium Forms Spec #29</t>
         </is>
       </c>
-      <c r="D190" s="6" t="n">
-        <v>0.12</v>
+      <c r="D190" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E190" s="4" t="inlineStr">
         <is>
@@ -4976,8 +5354,10 @@
           <t>Android Appium Forms Spec #30</t>
         </is>
       </c>
-      <c r="D191" s="6" t="n">
-        <v>0.04</v>
+      <c r="D191" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E191" s="4" t="inlineStr">
         <is>
@@ -4999,8 +5379,10 @@
           <t>Android Appium Forms Spec #31</t>
         </is>
       </c>
-      <c r="D192" s="6" t="n">
-        <v>0.06</v>
+      <c r="D192" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E192" s="4" t="inlineStr">
         <is>
@@ -5022,8 +5404,10 @@
           <t>Android Appium Forms Spec #32</t>
         </is>
       </c>
-      <c r="D193" s="6" t="n">
-        <v>0.08</v>
+      <c r="D193" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E193" s="4" t="inlineStr">
         <is>
@@ -5045,8 +5429,10 @@
           <t>Android Appium Forms Spec #33</t>
         </is>
       </c>
-      <c r="D194" s="6" t="n">
-        <v>0.1</v>
+      <c r="D194" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E194" s="4" t="inlineStr">
         <is>
@@ -5068,8 +5454,10 @@
           <t>Android Appium Forms Spec #34</t>
         </is>
       </c>
-      <c r="D195" s="6" t="n">
-        <v>0.12</v>
+      <c r="D195" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E195" s="4" t="inlineStr">
         <is>
@@ -5091,8 +5479,10 @@
           <t>Android Appium Forms Spec #35</t>
         </is>
       </c>
-      <c r="D196" s="6" t="n">
-        <v>0.04</v>
+      <c r="D196" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E196" s="4" t="inlineStr">
         <is>
@@ -5114,8 +5504,10 @@
           <t>Android Appium Forms Spec #36</t>
         </is>
       </c>
-      <c r="D197" s="6" t="n">
-        <v>0.06</v>
+      <c r="D197" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E197" s="4" t="inlineStr">
         <is>
@@ -5137,8 +5529,10 @@
           <t>Android Appium Forms Spec #37</t>
         </is>
       </c>
-      <c r="D198" s="6" t="n">
-        <v>0.08</v>
+      <c r="D198" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E198" s="4" t="inlineStr">
         <is>
@@ -5160,8 +5554,10 @@
           <t>Android Appium Forms Spec #38</t>
         </is>
       </c>
-      <c r="D199" s="6" t="n">
-        <v>0.1</v>
+      <c r="D199" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E199" s="4" t="inlineStr">
         <is>
@@ -5183,8 +5579,10 @@
           <t>Android Appium Forms Spec #39</t>
         </is>
       </c>
-      <c r="D200" s="6" t="n">
-        <v>0.12</v>
+      <c r="D200" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E200" s="4" t="inlineStr">
         <is>
@@ -5206,8 +5604,10 @@
           <t>Android Appium Forms Spec #40</t>
         </is>
       </c>
-      <c r="D201" s="6" t="n">
-        <v>0.04</v>
+      <c r="D201" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E201" s="4" t="inlineStr">
         <is>
@@ -5229,8 +5629,10 @@
           <t>Android Appium CRUD Operations Spec #01</t>
         </is>
       </c>
-      <c r="D202" s="6" t="n">
-        <v>0.06</v>
+      <c r="D202" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E202" s="4" t="inlineStr">
         <is>
@@ -5252,8 +5654,10 @@
           <t>Android Appium CRUD Operations Spec #02</t>
         </is>
       </c>
-      <c r="D203" s="6" t="n">
-        <v>0.08</v>
+      <c r="D203" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E203" s="4" t="inlineStr">
         <is>
@@ -5275,8 +5679,10 @@
           <t>Android Appium CRUD Operations Spec #03</t>
         </is>
       </c>
-      <c r="D204" s="6" t="n">
-        <v>0.1</v>
+      <c r="D204" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E204" s="4" t="inlineStr">
         <is>
@@ -5298,8 +5704,10 @@
           <t>Android Appium CRUD Operations Spec #04</t>
         </is>
       </c>
-      <c r="D205" s="6" t="n">
-        <v>0.12</v>
+      <c r="D205" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E205" s="4" t="inlineStr">
         <is>
@@ -5321,8 +5729,10 @@
           <t>Android Appium CRUD Operations Spec #05</t>
         </is>
       </c>
-      <c r="D206" s="6" t="n">
-        <v>0.04</v>
+      <c r="D206" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E206" s="4" t="inlineStr">
         <is>
@@ -5344,8 +5754,10 @@
           <t>Android Appium CRUD Operations Spec #06</t>
         </is>
       </c>
-      <c r="D207" s="6" t="n">
-        <v>0.06</v>
+      <c r="D207" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E207" s="4" t="inlineStr">
         <is>
@@ -5367,8 +5779,10 @@
           <t>Android Appium CRUD Operations Spec #07</t>
         </is>
       </c>
-      <c r="D208" s="6" t="n">
-        <v>0.08</v>
+      <c r="D208" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E208" s="4" t="inlineStr">
         <is>
@@ -5390,8 +5804,10 @@
           <t>Android Appium CRUD Operations Spec #08</t>
         </is>
       </c>
-      <c r="D209" s="6" t="n">
-        <v>0.1</v>
+      <c r="D209" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E209" s="4" t="inlineStr">
         <is>
@@ -5413,8 +5829,10 @@
           <t>Android Appium CRUD Operations Spec #09</t>
         </is>
       </c>
-      <c r="D210" s="6" t="n">
-        <v>0.12</v>
+      <c r="D210" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E210" s="4" t="inlineStr">
         <is>
@@ -5436,8 +5854,10 @@
           <t>Android Appium CRUD Operations Spec #10</t>
         </is>
       </c>
-      <c r="D211" s="6" t="n">
-        <v>0.04</v>
+      <c r="D211" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E211" s="4" t="inlineStr">
         <is>
@@ -5459,8 +5879,10 @@
           <t>Android Appium CRUD Operations Spec #11</t>
         </is>
       </c>
-      <c r="D212" s="6" t="n">
-        <v>0.06</v>
+      <c r="D212" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E212" s="4" t="inlineStr">
         <is>
@@ -5482,8 +5904,10 @@
           <t>Android Appium CRUD Operations Spec #12</t>
         </is>
       </c>
-      <c r="D213" s="6" t="n">
-        <v>0.08</v>
+      <c r="D213" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E213" s="4" t="inlineStr">
         <is>
@@ -5505,8 +5929,10 @@
           <t>Android Appium CRUD Operations Spec #13</t>
         </is>
       </c>
-      <c r="D214" s="6" t="n">
-        <v>0.1</v>
+      <c r="D214" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E214" s="4" t="inlineStr">
         <is>
@@ -5528,8 +5954,10 @@
           <t>Android Appium CRUD Operations Spec #14</t>
         </is>
       </c>
-      <c r="D215" s="6" t="n">
-        <v>0.12</v>
+      <c r="D215" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E215" s="4" t="inlineStr">
         <is>
@@ -5551,8 +5979,10 @@
           <t>Android Appium CRUD Operations Spec #15</t>
         </is>
       </c>
-      <c r="D216" s="6" t="n">
-        <v>0.04</v>
+      <c r="D216" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E216" s="4" t="inlineStr">
         <is>
@@ -5574,8 +6004,10 @@
           <t>Android Appium CRUD Operations Spec #16</t>
         </is>
       </c>
-      <c r="D217" s="6" t="n">
-        <v>0.06</v>
+      <c r="D217" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E217" s="4" t="inlineStr">
         <is>
@@ -5597,8 +6029,10 @@
           <t>Android Appium CRUD Operations Spec #17</t>
         </is>
       </c>
-      <c r="D218" s="6" t="n">
-        <v>0.08</v>
+      <c r="D218" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E218" s="4" t="inlineStr">
         <is>
@@ -5620,8 +6054,10 @@
           <t>Android Appium CRUD Operations Spec #18</t>
         </is>
       </c>
-      <c r="D219" s="6" t="n">
-        <v>0.1</v>
+      <c r="D219" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E219" s="4" t="inlineStr">
         <is>
@@ -5643,8 +6079,10 @@
           <t>Android Appium CRUD Operations Spec #19</t>
         </is>
       </c>
-      <c r="D220" s="6" t="n">
-        <v>0.12</v>
+      <c r="D220" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E220" s="4" t="inlineStr">
         <is>
@@ -5666,8 +6104,10 @@
           <t>Android Appium CRUD Operations Spec #20</t>
         </is>
       </c>
-      <c r="D221" s="6" t="n">
-        <v>0.04</v>
+      <c r="D221" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E221" s="4" t="inlineStr">
         <is>
@@ -5689,8 +6129,10 @@
           <t>Android Appium CRUD Operations Spec #21</t>
         </is>
       </c>
-      <c r="D222" s="6" t="n">
-        <v>0.06</v>
+      <c r="D222" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E222" s="4" t="inlineStr">
         <is>
@@ -5712,8 +6154,10 @@
           <t>Android Appium CRUD Operations Spec #22</t>
         </is>
       </c>
-      <c r="D223" s="6" t="n">
-        <v>0.08</v>
+      <c r="D223" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E223" s="4" t="inlineStr">
         <is>
@@ -5735,8 +6179,10 @@
           <t>Android Appium CRUD Operations Spec #23</t>
         </is>
       </c>
-      <c r="D224" s="6" t="n">
-        <v>0.1</v>
+      <c r="D224" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E224" s="4" t="inlineStr">
         <is>
@@ -5758,8 +6204,10 @@
           <t>Android Appium CRUD Operations Spec #24</t>
         </is>
       </c>
-      <c r="D225" s="6" t="n">
-        <v>0.12</v>
+      <c r="D225" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E225" s="4" t="inlineStr">
         <is>
@@ -5781,8 +6229,10 @@
           <t>Android Appium CRUD Operations Spec #25</t>
         </is>
       </c>
-      <c r="D226" s="6" t="n">
-        <v>0.04</v>
+      <c r="D226" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E226" s="4" t="inlineStr">
         <is>
@@ -5804,8 +6254,10 @@
           <t>Android Appium CRUD Operations Spec #26</t>
         </is>
       </c>
-      <c r="D227" s="6" t="n">
-        <v>0.06</v>
+      <c r="D227" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E227" s="4" t="inlineStr">
         <is>
@@ -5827,8 +6279,10 @@
           <t>Android Appium CRUD Operations Spec #27</t>
         </is>
       </c>
-      <c r="D228" s="6" t="n">
-        <v>0.08</v>
+      <c r="D228" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E228" s="4" t="inlineStr">
         <is>
@@ -5850,8 +6304,10 @@
           <t>Android Appium CRUD Operations Spec #28</t>
         </is>
       </c>
-      <c r="D229" s="6" t="n">
-        <v>0.1</v>
+      <c r="D229" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E229" s="4" t="inlineStr">
         <is>
@@ -5873,8 +6329,10 @@
           <t>Android Appium CRUD Operations Spec #29</t>
         </is>
       </c>
-      <c r="D230" s="6" t="n">
-        <v>0.12</v>
+      <c r="D230" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E230" s="4" t="inlineStr">
         <is>
@@ -5896,8 +6354,10 @@
           <t>Android Appium CRUD Operations Spec #30</t>
         </is>
       </c>
-      <c r="D231" s="6" t="n">
-        <v>0.04</v>
+      <c r="D231" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E231" s="4" t="inlineStr">
         <is>
@@ -5919,8 +6379,10 @@
           <t>Android Appium CRUD Operations Spec #31</t>
         </is>
       </c>
-      <c r="D232" s="6" t="n">
-        <v>0.06</v>
+      <c r="D232" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E232" s="4" t="inlineStr">
         <is>
@@ -5942,8 +6404,10 @@
           <t>Android Appium CRUD Operations Spec #32</t>
         </is>
       </c>
-      <c r="D233" s="6" t="n">
-        <v>0.08</v>
+      <c r="D233" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E233" s="4" t="inlineStr">
         <is>
@@ -5965,8 +6429,10 @@
           <t>Android Appium CRUD Operations Spec #33</t>
         </is>
       </c>
-      <c r="D234" s="6" t="n">
-        <v>0.1</v>
+      <c r="D234" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E234" s="4" t="inlineStr">
         <is>
@@ -5988,8 +6454,10 @@
           <t>Android Appium CRUD Operations Spec #34</t>
         </is>
       </c>
-      <c r="D235" s="6" t="n">
-        <v>0.12</v>
+      <c r="D235" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E235" s="4" t="inlineStr">
         <is>
@@ -6011,8 +6479,10 @@
           <t>Android Appium CRUD Operations Spec #35</t>
         </is>
       </c>
-      <c r="D236" s="6" t="n">
-        <v>0.04</v>
+      <c r="D236" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E236" s="4" t="inlineStr">
         <is>
@@ -6034,8 +6504,10 @@
           <t>Android Appium CRUD Operations Spec #36</t>
         </is>
       </c>
-      <c r="D237" s="6" t="n">
-        <v>0.06</v>
+      <c r="D237" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E237" s="4" t="inlineStr">
         <is>
@@ -6057,8 +6529,10 @@
           <t>Android Appium CRUD Operations Spec #37</t>
         </is>
       </c>
-      <c r="D238" s="6" t="n">
-        <v>0.08</v>
+      <c r="D238" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E238" s="4" t="inlineStr">
         <is>
@@ -6080,8 +6554,10 @@
           <t>Android Appium CRUD Operations Spec #38</t>
         </is>
       </c>
-      <c r="D239" s="6" t="n">
-        <v>0.1</v>
+      <c r="D239" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E239" s="4" t="inlineStr">
         <is>
@@ -6103,8 +6579,10 @@
           <t>Android Appium CRUD Operations Spec #39</t>
         </is>
       </c>
-      <c r="D240" s="6" t="n">
-        <v>0.12</v>
+      <c r="D240" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E240" s="4" t="inlineStr">
         <is>
@@ -6126,8 +6604,10 @@
           <t>Android Appium CRUD Operations Spec #40</t>
         </is>
       </c>
-      <c r="D241" s="6" t="n">
-        <v>0.04</v>
+      <c r="D241" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E241" s="4" t="inlineStr">
         <is>
@@ -6149,8 +6629,10 @@
           <t>Android Appium Search Spec #01</t>
         </is>
       </c>
-      <c r="D242" s="6" t="n">
-        <v>0.06</v>
+      <c r="D242" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E242" s="4" t="inlineStr">
         <is>
@@ -6172,8 +6654,10 @@
           <t>Android Appium Search Spec #02</t>
         </is>
       </c>
-      <c r="D243" s="6" t="n">
-        <v>0.08</v>
+      <c r="D243" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E243" s="4" t="inlineStr">
         <is>
@@ -6195,8 +6679,10 @@
           <t>Android Appium Search Spec #03</t>
         </is>
       </c>
-      <c r="D244" s="6" t="n">
-        <v>0.1</v>
+      <c r="D244" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E244" s="4" t="inlineStr">
         <is>
@@ -6218,8 +6704,10 @@
           <t>Android Appium Search Spec #04</t>
         </is>
       </c>
-      <c r="D245" s="6" t="n">
-        <v>0.12</v>
+      <c r="D245" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E245" s="4" t="inlineStr">
         <is>
@@ -6241,8 +6729,10 @@
           <t>Android Appium Search Spec #05</t>
         </is>
       </c>
-      <c r="D246" s="6" t="n">
-        <v>0.04</v>
+      <c r="D246" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E246" s="4" t="inlineStr">
         <is>
@@ -6264,8 +6754,10 @@
           <t>Android Appium Search Spec #06</t>
         </is>
       </c>
-      <c r="D247" s="6" t="n">
-        <v>0.06</v>
+      <c r="D247" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E247" s="4" t="inlineStr">
         <is>
@@ -6287,8 +6779,10 @@
           <t>Android Appium Search Spec #07</t>
         </is>
       </c>
-      <c r="D248" s="6" t="n">
-        <v>0.08</v>
+      <c r="D248" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E248" s="4" t="inlineStr">
         <is>
@@ -6310,8 +6804,10 @@
           <t>Android Appium Search Spec #08</t>
         </is>
       </c>
-      <c r="D249" s="6" t="n">
-        <v>0.1</v>
+      <c r="D249" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E249" s="4" t="inlineStr">
         <is>
@@ -6333,8 +6829,10 @@
           <t>Android Appium Search Spec #09</t>
         </is>
       </c>
-      <c r="D250" s="6" t="n">
-        <v>0.12</v>
+      <c r="D250" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E250" s="4" t="inlineStr">
         <is>
@@ -6356,8 +6854,10 @@
           <t>Android Appium Search Spec #10</t>
         </is>
       </c>
-      <c r="D251" s="6" t="n">
-        <v>0.04</v>
+      <c r="D251" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E251" s="4" t="inlineStr">
         <is>
@@ -6379,8 +6879,10 @@
           <t>Android Appium Search Spec #11</t>
         </is>
       </c>
-      <c r="D252" s="6" t="n">
-        <v>0.06</v>
+      <c r="D252" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E252" s="4" t="inlineStr">
         <is>
@@ -6402,8 +6904,10 @@
           <t>Android Appium Search Spec #12</t>
         </is>
       </c>
-      <c r="D253" s="6" t="n">
-        <v>0.08</v>
+      <c r="D253" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E253" s="4" t="inlineStr">
         <is>
@@ -6425,8 +6929,10 @@
           <t>Android Appium Search Spec #13</t>
         </is>
       </c>
-      <c r="D254" s="6" t="n">
-        <v>0.1</v>
+      <c r="D254" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E254" s="4" t="inlineStr">
         <is>
@@ -6448,8 +6954,10 @@
           <t>Android Appium Search Spec #14</t>
         </is>
       </c>
-      <c r="D255" s="6" t="n">
-        <v>0.12</v>
+      <c r="D255" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E255" s="4" t="inlineStr">
         <is>
@@ -6471,8 +6979,10 @@
           <t>Android Appium Search Spec #15</t>
         </is>
       </c>
-      <c r="D256" s="6" t="n">
-        <v>0.04</v>
+      <c r="D256" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E256" s="4" t="inlineStr">
         <is>
@@ -6494,8 +7004,10 @@
           <t>Android Appium Search Spec #16</t>
         </is>
       </c>
-      <c r="D257" s="6" t="n">
-        <v>0.06</v>
+      <c r="D257" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E257" s="4" t="inlineStr">
         <is>
@@ -6517,8 +7029,10 @@
           <t>Android Appium Search Spec #17</t>
         </is>
       </c>
-      <c r="D258" s="6" t="n">
-        <v>0.08</v>
+      <c r="D258" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E258" s="4" t="inlineStr">
         <is>
@@ -6540,8 +7054,10 @@
           <t>Android Appium Search Spec #18</t>
         </is>
       </c>
-      <c r="D259" s="6" t="n">
-        <v>0.1</v>
+      <c r="D259" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E259" s="4" t="inlineStr">
         <is>
@@ -6563,8 +7079,10 @@
           <t>Android Appium Search Spec #19</t>
         </is>
       </c>
-      <c r="D260" s="6" t="n">
-        <v>0.12</v>
+      <c r="D260" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E260" s="4" t="inlineStr">
         <is>
@@ -6586,8 +7104,10 @@
           <t>Android Appium Search Spec #20</t>
         </is>
       </c>
-      <c r="D261" s="6" t="n">
-        <v>0.04</v>
+      <c r="D261" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E261" s="4" t="inlineStr">
         <is>
@@ -6609,8 +7129,10 @@
           <t>Android Appium Filters Spec #01</t>
         </is>
       </c>
-      <c r="D262" s="6" t="n">
-        <v>0.06</v>
+      <c r="D262" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E262" s="4" t="inlineStr">
         <is>
@@ -6632,8 +7154,10 @@
           <t>Android Appium Filters Spec #02</t>
         </is>
       </c>
-      <c r="D263" s="6" t="n">
-        <v>0.08</v>
+      <c r="D263" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E263" s="4" t="inlineStr">
         <is>
@@ -6655,8 +7179,10 @@
           <t>Android Appium Filters Spec #03</t>
         </is>
       </c>
-      <c r="D264" s="6" t="n">
-        <v>0.1</v>
+      <c r="D264" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E264" s="4" t="inlineStr">
         <is>
@@ -6678,8 +7204,10 @@
           <t>Android Appium Filters Spec #04</t>
         </is>
       </c>
-      <c r="D265" s="6" t="n">
-        <v>0.12</v>
+      <c r="D265" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E265" s="4" t="inlineStr">
         <is>
@@ -6701,8 +7229,10 @@
           <t>Android Appium Filters Spec #05</t>
         </is>
       </c>
-      <c r="D266" s="6" t="n">
-        <v>0.04</v>
+      <c r="D266" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E266" s="4" t="inlineStr">
         <is>
@@ -6724,8 +7254,10 @@
           <t>Android Appium Filters Spec #06</t>
         </is>
       </c>
-      <c r="D267" s="6" t="n">
-        <v>0.06</v>
+      <c r="D267" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E267" s="4" t="inlineStr">
         <is>
@@ -6747,8 +7279,10 @@
           <t>Android Appium Filters Spec #07</t>
         </is>
       </c>
-      <c r="D268" s="6" t="n">
-        <v>0.08</v>
+      <c r="D268" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E268" s="4" t="inlineStr">
         <is>
@@ -6770,8 +7304,10 @@
           <t>Android Appium Filters Spec #08</t>
         </is>
       </c>
-      <c r="D269" s="6" t="n">
-        <v>0.1</v>
+      <c r="D269" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E269" s="4" t="inlineStr">
         <is>
@@ -6793,8 +7329,10 @@
           <t>Android Appium Filters Spec #09</t>
         </is>
       </c>
-      <c r="D270" s="6" t="n">
-        <v>0.12</v>
+      <c r="D270" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E270" s="4" t="inlineStr">
         <is>
@@ -6816,8 +7354,10 @@
           <t>Android Appium Filters Spec #10</t>
         </is>
       </c>
-      <c r="D271" s="6" t="n">
-        <v>0.04</v>
+      <c r="D271" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E271" s="4" t="inlineStr">
         <is>
@@ -6839,8 +7379,10 @@
           <t>Android Appium Filters Spec #11</t>
         </is>
       </c>
-      <c r="D272" s="6" t="n">
-        <v>0.06</v>
+      <c r="D272" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E272" s="4" t="inlineStr">
         <is>
@@ -6862,8 +7404,10 @@
           <t>Android Appium Filters Spec #12</t>
         </is>
       </c>
-      <c r="D273" s="6" t="n">
-        <v>0.08</v>
+      <c r="D273" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E273" s="4" t="inlineStr">
         <is>
@@ -6885,8 +7429,10 @@
           <t>Android Appium Filters Spec #13</t>
         </is>
       </c>
-      <c r="D274" s="6" t="n">
-        <v>0.1</v>
+      <c r="D274" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E274" s="4" t="inlineStr">
         <is>
@@ -6908,8 +7454,10 @@
           <t>Android Appium Filters Spec #14</t>
         </is>
       </c>
-      <c r="D275" s="6" t="n">
-        <v>0.12</v>
+      <c r="D275" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E275" s="4" t="inlineStr">
         <is>
@@ -6931,8 +7479,10 @@
           <t>Android Appium Filters Spec #15</t>
         </is>
       </c>
-      <c r="D276" s="6" t="n">
-        <v>0.04</v>
+      <c r="D276" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E276" s="4" t="inlineStr">
         <is>
@@ -6954,8 +7504,10 @@
           <t>Android Appium Filters Spec #16</t>
         </is>
       </c>
-      <c r="D277" s="6" t="n">
-        <v>0.06</v>
+      <c r="D277" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E277" s="4" t="inlineStr">
         <is>
@@ -6977,8 +7529,10 @@
           <t>Android Appium Filters Spec #17</t>
         </is>
       </c>
-      <c r="D278" s="6" t="n">
-        <v>0.08</v>
+      <c r="D278" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E278" s="4" t="inlineStr">
         <is>
@@ -7000,8 +7554,10 @@
           <t>Android Appium Filters Spec #18</t>
         </is>
       </c>
-      <c r="D279" s="6" t="n">
-        <v>0.1</v>
+      <c r="D279" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E279" s="4" t="inlineStr">
         <is>
@@ -7023,8 +7579,10 @@
           <t>Android Appium Filters Spec #19</t>
         </is>
       </c>
-      <c r="D280" s="6" t="n">
-        <v>0.12</v>
+      <c r="D280" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E280" s="4" t="inlineStr">
         <is>
@@ -7046,8 +7604,10 @@
           <t>Android Appium Filters Spec #20</t>
         </is>
       </c>
-      <c r="D281" s="6" t="n">
-        <v>0.04</v>
+      <c r="D281" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E281" s="4" t="inlineStr">
         <is>
@@ -7069,8 +7629,10 @@
           <t>Android Appium Input Validation Spec #01</t>
         </is>
       </c>
-      <c r="D282" s="6" t="n">
-        <v>0.06</v>
+      <c r="D282" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E282" s="4" t="inlineStr">
         <is>
@@ -7092,8 +7654,10 @@
           <t>Android Appium Input Validation Spec #02</t>
         </is>
       </c>
-      <c r="D283" s="6" t="n">
-        <v>0.08</v>
+      <c r="D283" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E283" s="4" t="inlineStr">
         <is>
@@ -7115,8 +7679,10 @@
           <t>Android Appium Input Validation Spec #03</t>
         </is>
       </c>
-      <c r="D284" s="6" t="n">
-        <v>0.1</v>
+      <c r="D284" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E284" s="4" t="inlineStr">
         <is>
@@ -7138,8 +7704,10 @@
           <t>Android Appium Input Validation Spec #04</t>
         </is>
       </c>
-      <c r="D285" s="6" t="n">
-        <v>0.12</v>
+      <c r="D285" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E285" s="4" t="inlineStr">
         <is>
@@ -7161,8 +7729,10 @@
           <t>Android Appium Input Validation Spec #05</t>
         </is>
       </c>
-      <c r="D286" s="6" t="n">
-        <v>0.04</v>
+      <c r="D286" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E286" s="4" t="inlineStr">
         <is>
@@ -7184,8 +7754,10 @@
           <t>Android Appium Input Validation Spec #06</t>
         </is>
       </c>
-      <c r="D287" s="6" t="n">
-        <v>0.06</v>
+      <c r="D287" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E287" s="4" t="inlineStr">
         <is>
@@ -7207,8 +7779,10 @@
           <t>Android Appium Input Validation Spec #07</t>
         </is>
       </c>
-      <c r="D288" s="6" t="n">
-        <v>0.08</v>
+      <c r="D288" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E288" s="4" t="inlineStr">
         <is>
@@ -7230,8 +7804,10 @@
           <t>Android Appium Input Validation Spec #08</t>
         </is>
       </c>
-      <c r="D289" s="6" t="n">
-        <v>0.1</v>
+      <c r="D289" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E289" s="4" t="inlineStr">
         <is>
@@ -7253,8 +7829,10 @@
           <t>Android Appium Input Validation Spec #09</t>
         </is>
       </c>
-      <c r="D290" s="6" t="n">
-        <v>0.12</v>
+      <c r="D290" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E290" s="4" t="inlineStr">
         <is>
@@ -7276,8 +7854,10 @@
           <t>Android Appium Input Validation Spec #10</t>
         </is>
       </c>
-      <c r="D291" s="6" t="n">
-        <v>0.04</v>
+      <c r="D291" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E291" s="4" t="inlineStr">
         <is>
@@ -7299,8 +7879,10 @@
           <t>Android Appium Input Validation Spec #11</t>
         </is>
       </c>
-      <c r="D292" s="6" t="n">
-        <v>0.06</v>
+      <c r="D292" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E292" s="4" t="inlineStr">
         <is>
@@ -7322,8 +7904,10 @@
           <t>Android Appium Input Validation Spec #12</t>
         </is>
       </c>
-      <c r="D293" s="6" t="n">
-        <v>0.08</v>
+      <c r="D293" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E293" s="4" t="inlineStr">
         <is>
@@ -7345,8 +7929,10 @@
           <t>Android Appium Input Validation Spec #13</t>
         </is>
       </c>
-      <c r="D294" s="6" t="n">
-        <v>0.1</v>
+      <c r="D294" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E294" s="4" t="inlineStr">
         <is>
@@ -7368,8 +7954,10 @@
           <t>Android Appium Input Validation Spec #14</t>
         </is>
       </c>
-      <c r="D295" s="6" t="n">
-        <v>0.12</v>
+      <c r="D295" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E295" s="4" t="inlineStr">
         <is>
@@ -7391,8 +7979,10 @@
           <t>Android Appium Input Validation Spec #15</t>
         </is>
       </c>
-      <c r="D296" s="6" t="n">
-        <v>0.04</v>
+      <c r="D296" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E296" s="4" t="inlineStr">
         <is>
@@ -7414,8 +8004,10 @@
           <t>Android Appium Input Validation Spec #16</t>
         </is>
       </c>
-      <c r="D297" s="6" t="n">
-        <v>0.06</v>
+      <c r="D297" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E297" s="4" t="inlineStr">
         <is>
@@ -7437,8 +8029,10 @@
           <t>Android Appium Input Validation Spec #17</t>
         </is>
       </c>
-      <c r="D298" s="6" t="n">
-        <v>0.08</v>
+      <c r="D298" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E298" s="4" t="inlineStr">
         <is>
@@ -7460,8 +8054,10 @@
           <t>Android Appium Input Validation Spec #18</t>
         </is>
       </c>
-      <c r="D299" s="6" t="n">
-        <v>0.1</v>
+      <c r="D299" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E299" s="4" t="inlineStr">
         <is>
@@ -7483,8 +8079,10 @@
           <t>Android Appium Input Validation Spec #19</t>
         </is>
       </c>
-      <c r="D300" s="6" t="n">
-        <v>0.12</v>
+      <c r="D300" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E300" s="4" t="inlineStr">
         <is>
@@ -7506,8 +8104,10 @@
           <t>Android Appium Input Validation Spec #20</t>
         </is>
       </c>
-      <c r="D301" s="6" t="n">
-        <v>0.04</v>
+      <c r="D301" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E301" s="4" t="inlineStr">
         <is>
@@ -7529,8 +8129,10 @@
           <t>Android Appium Input Validation Spec #21</t>
         </is>
       </c>
-      <c r="D302" s="6" t="n">
-        <v>0.06</v>
+      <c r="D302" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E302" s="4" t="inlineStr">
         <is>
@@ -7552,8 +8154,10 @@
           <t>Android Appium Input Validation Spec #22</t>
         </is>
       </c>
-      <c r="D303" s="6" t="n">
-        <v>0.08</v>
+      <c r="D303" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E303" s="4" t="inlineStr">
         <is>
@@ -7575,8 +8179,10 @@
           <t>Android Appium Input Validation Spec #23</t>
         </is>
       </c>
-      <c r="D304" s="6" t="n">
-        <v>0.1</v>
+      <c r="D304" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E304" s="4" t="inlineStr">
         <is>
@@ -7598,8 +8204,10 @@
           <t>Android Appium Input Validation Spec #24</t>
         </is>
       </c>
-      <c r="D305" s="6" t="n">
-        <v>0.12</v>
+      <c r="D305" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E305" s="4" t="inlineStr">
         <is>
@@ -7621,8 +8229,10 @@
           <t>Android Appium Input Validation Spec #25</t>
         </is>
       </c>
-      <c r="D306" s="6" t="n">
-        <v>0.04</v>
+      <c r="D306" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E306" s="4" t="inlineStr">
         <is>
@@ -7644,8 +8254,10 @@
           <t>Android Appium Input Validation Spec #26</t>
         </is>
       </c>
-      <c r="D307" s="6" t="n">
-        <v>0.06</v>
+      <c r="D307" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E307" s="4" t="inlineStr">
         <is>
@@ -7667,8 +8279,10 @@
           <t>Android Appium Input Validation Spec #27</t>
         </is>
       </c>
-      <c r="D308" s="6" t="n">
-        <v>0.08</v>
+      <c r="D308" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E308" s="4" t="inlineStr">
         <is>
@@ -7690,8 +8304,10 @@
           <t>Android Appium Input Validation Spec #28</t>
         </is>
       </c>
-      <c r="D309" s="6" t="n">
-        <v>0.1</v>
+      <c r="D309" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E309" s="4" t="inlineStr">
         <is>
@@ -7713,8 +8329,10 @@
           <t>Android Appium Input Validation Spec #29</t>
         </is>
       </c>
-      <c r="D310" s="6" t="n">
-        <v>0.12</v>
+      <c r="D310" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E310" s="4" t="inlineStr">
         <is>
@@ -7736,8 +8354,10 @@
           <t>Android Appium Input Validation Spec #30</t>
         </is>
       </c>
-      <c r="D311" s="6" t="n">
-        <v>0.04</v>
+      <c r="D311" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E311" s="4" t="inlineStr">
         <is>
@@ -7759,8 +8379,10 @@
           <t>Android Appium Input Validation Spec #31</t>
         </is>
       </c>
-      <c r="D312" s="6" t="n">
-        <v>0.06</v>
+      <c r="D312" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E312" s="4" t="inlineStr">
         <is>
@@ -7782,8 +8404,10 @@
           <t>Android Appium Input Validation Spec #32</t>
         </is>
       </c>
-      <c r="D313" s="6" t="n">
-        <v>0.08</v>
+      <c r="D313" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E313" s="4" t="inlineStr">
         <is>
@@ -7805,8 +8429,10 @@
           <t>Android Appium Input Validation Spec #33</t>
         </is>
       </c>
-      <c r="D314" s="6" t="n">
-        <v>0.1</v>
+      <c r="D314" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E314" s="4" t="inlineStr">
         <is>
@@ -7828,8 +8454,10 @@
           <t>Android Appium Input Validation Spec #34</t>
         </is>
       </c>
-      <c r="D315" s="6" t="n">
-        <v>0.12</v>
+      <c r="D315" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E315" s="4" t="inlineStr">
         <is>
@@ -7851,8 +8479,10 @@
           <t>Android Appium Input Validation Spec #35</t>
         </is>
       </c>
-      <c r="D316" s="6" t="n">
-        <v>0.04</v>
+      <c r="D316" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E316" s="4" t="inlineStr">
         <is>
@@ -7874,8 +8504,10 @@
           <t>Android Appium Input Validation Spec #36</t>
         </is>
       </c>
-      <c r="D317" s="6" t="n">
-        <v>0.06</v>
+      <c r="D317" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E317" s="4" t="inlineStr">
         <is>
@@ -7897,8 +8529,10 @@
           <t>Android Appium Input Validation Spec #37</t>
         </is>
       </c>
-      <c r="D318" s="6" t="n">
-        <v>0.08</v>
+      <c r="D318" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E318" s="4" t="inlineStr">
         <is>
@@ -7920,8 +8554,10 @@
           <t>Android Appium Input Validation Spec #38</t>
         </is>
       </c>
-      <c r="D319" s="6" t="n">
-        <v>0.1</v>
+      <c r="D319" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E319" s="4" t="inlineStr">
         <is>
@@ -7943,8 +8579,10 @@
           <t>Android Appium Input Validation Spec #39</t>
         </is>
       </c>
-      <c r="D320" s="6" t="n">
-        <v>0.12</v>
+      <c r="D320" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E320" s="4" t="inlineStr">
         <is>
@@ -7966,8 +8604,10 @@
           <t>Android Appium Input Validation Spec #40</t>
         </is>
       </c>
-      <c r="D321" s="6" t="n">
-        <v>0.04</v>
+      <c r="D321" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E321" s="4" t="inlineStr">
         <is>
@@ -7989,8 +8629,10 @@
           <t>Android Appium Error Handling Spec #01</t>
         </is>
       </c>
-      <c r="D322" s="6" t="n">
-        <v>0.06</v>
+      <c r="D322" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E322" s="4" t="inlineStr">
         <is>
@@ -8012,8 +8654,10 @@
           <t>Android Appium Error Handling Spec #02</t>
         </is>
       </c>
-      <c r="D323" s="6" t="n">
-        <v>0.08</v>
+      <c r="D323" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E323" s="4" t="inlineStr">
         <is>
@@ -8035,8 +8679,10 @@
           <t>Android Appium Error Handling Spec #03</t>
         </is>
       </c>
-      <c r="D324" s="6" t="n">
-        <v>0.1</v>
+      <c r="D324" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E324" s="4" t="inlineStr">
         <is>
@@ -8058,8 +8704,10 @@
           <t>Android Appium Error Handling Spec #04</t>
         </is>
       </c>
-      <c r="D325" s="6" t="n">
-        <v>0.12</v>
+      <c r="D325" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E325" s="4" t="inlineStr">
         <is>
@@ -8081,8 +8729,10 @@
           <t>Android Appium Error Handling Spec #05</t>
         </is>
       </c>
-      <c r="D326" s="6" t="n">
-        <v>0.04</v>
+      <c r="D326" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E326" s="4" t="inlineStr">
         <is>
@@ -8104,8 +8754,10 @@
           <t>Android Appium Error Handling Spec #06</t>
         </is>
       </c>
-      <c r="D327" s="6" t="n">
-        <v>0.06</v>
+      <c r="D327" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E327" s="4" t="inlineStr">
         <is>
@@ -8127,8 +8779,10 @@
           <t>Android Appium Error Handling Spec #07</t>
         </is>
       </c>
-      <c r="D328" s="6" t="n">
-        <v>0.08</v>
+      <c r="D328" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E328" s="4" t="inlineStr">
         <is>
@@ -8150,8 +8804,10 @@
           <t>Android Appium Error Handling Spec #08</t>
         </is>
       </c>
-      <c r="D329" s="6" t="n">
-        <v>0.1</v>
+      <c r="D329" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E329" s="4" t="inlineStr">
         <is>
@@ -8173,8 +8829,10 @@
           <t>Android Appium Error Handling Spec #09</t>
         </is>
       </c>
-      <c r="D330" s="6" t="n">
-        <v>0.12</v>
+      <c r="D330" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E330" s="4" t="inlineStr">
         <is>
@@ -8196,8 +8854,10 @@
           <t>Android Appium Error Handling Spec #10</t>
         </is>
       </c>
-      <c r="D331" s="6" t="n">
-        <v>0.04</v>
+      <c r="D331" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E331" s="4" t="inlineStr">
         <is>
@@ -8219,8 +8879,10 @@
           <t>Android Appium Error Handling Spec #11</t>
         </is>
       </c>
-      <c r="D332" s="6" t="n">
-        <v>0.06</v>
+      <c r="D332" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E332" s="4" t="inlineStr">
         <is>
@@ -8242,8 +8904,10 @@
           <t>Android Appium Error Handling Spec #12</t>
         </is>
       </c>
-      <c r="D333" s="6" t="n">
-        <v>0.08</v>
+      <c r="D333" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E333" s="4" t="inlineStr">
         <is>
@@ -8265,8 +8929,10 @@
           <t>Android Appium Error Handling Spec #13</t>
         </is>
       </c>
-      <c r="D334" s="6" t="n">
-        <v>0.1</v>
+      <c r="D334" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E334" s="4" t="inlineStr">
         <is>
@@ -8288,8 +8954,10 @@
           <t>Android Appium Error Handling Spec #14</t>
         </is>
       </c>
-      <c r="D335" s="6" t="n">
-        <v>0.12</v>
+      <c r="D335" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E335" s="4" t="inlineStr">
         <is>
@@ -8311,8 +8979,10 @@
           <t>Android Appium Error Handling Spec #15</t>
         </is>
       </c>
-      <c r="D336" s="6" t="n">
-        <v>0.04</v>
+      <c r="D336" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E336" s="4" t="inlineStr">
         <is>
@@ -8334,8 +9004,10 @@
           <t>Android Appium Error Handling Spec #16</t>
         </is>
       </c>
-      <c r="D337" s="6" t="n">
-        <v>0.06</v>
+      <c r="D337" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E337" s="4" t="inlineStr">
         <is>
@@ -8357,8 +9029,10 @@
           <t>Android Appium Error Handling Spec #17</t>
         </is>
       </c>
-      <c r="D338" s="6" t="n">
-        <v>0.08</v>
+      <c r="D338" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E338" s="4" t="inlineStr">
         <is>
@@ -8380,8 +9054,10 @@
           <t>Android Appium Error Handling Spec #18</t>
         </is>
       </c>
-      <c r="D339" s="6" t="n">
-        <v>0.1</v>
+      <c r="D339" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E339" s="4" t="inlineStr">
         <is>
@@ -8403,8 +9079,10 @@
           <t>Android Appium Error Handling Spec #19</t>
         </is>
       </c>
-      <c r="D340" s="6" t="n">
-        <v>0.12</v>
+      <c r="D340" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E340" s="4" t="inlineStr">
         <is>
@@ -8426,8 +9104,10 @@
           <t>Android Appium Error Handling Spec #20</t>
         </is>
       </c>
-      <c r="D341" s="6" t="n">
-        <v>0.04</v>
+      <c r="D341" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E341" s="4" t="inlineStr">
         <is>
@@ -8449,8 +9129,10 @@
           <t>Android Appium Session Management Spec #01</t>
         </is>
       </c>
-      <c r="D342" s="6" t="n">
-        <v>0.06</v>
+      <c r="D342" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E342" s="4" t="inlineStr">
         <is>
@@ -8472,8 +9154,10 @@
           <t>Android Appium Session Management Spec #02</t>
         </is>
       </c>
-      <c r="D343" s="6" t="n">
-        <v>0.08</v>
+      <c r="D343" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E343" s="4" t="inlineStr">
         <is>
@@ -8495,8 +9179,10 @@
           <t>Android Appium Session Management Spec #03</t>
         </is>
       </c>
-      <c r="D344" s="6" t="n">
-        <v>0.1</v>
+      <c r="D344" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E344" s="4" t="inlineStr">
         <is>
@@ -8518,8 +9204,10 @@
           <t>Android Appium Session Management Spec #04</t>
         </is>
       </c>
-      <c r="D345" s="6" t="n">
-        <v>0.12</v>
+      <c r="D345" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E345" s="4" t="inlineStr">
         <is>
@@ -8541,8 +9229,10 @@
           <t>Android Appium Session Management Spec #05</t>
         </is>
       </c>
-      <c r="D346" s="6" t="n">
-        <v>0.04</v>
+      <c r="D346" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E346" s="4" t="inlineStr">
         <is>
@@ -8564,8 +9254,10 @@
           <t>Android Appium Session Management Spec #06</t>
         </is>
       </c>
-      <c r="D347" s="6" t="n">
-        <v>0.06</v>
+      <c r="D347" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E347" s="4" t="inlineStr">
         <is>
@@ -8587,8 +9279,10 @@
           <t>Android Appium Session Management Spec #07</t>
         </is>
       </c>
-      <c r="D348" s="6" t="n">
-        <v>0.08</v>
+      <c r="D348" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E348" s="4" t="inlineStr">
         <is>
@@ -8610,8 +9304,10 @@
           <t>Android Appium Session Management Spec #08</t>
         </is>
       </c>
-      <c r="D349" s="6" t="n">
-        <v>0.1</v>
+      <c r="D349" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E349" s="4" t="inlineStr">
         <is>
@@ -8633,8 +9329,10 @@
           <t>Android Appium Session Management Spec #09</t>
         </is>
       </c>
-      <c r="D350" s="6" t="n">
-        <v>0.12</v>
+      <c r="D350" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E350" s="4" t="inlineStr">
         <is>
@@ -8656,8 +9354,10 @@
           <t>Android Appium Session Management Spec #10</t>
         </is>
       </c>
-      <c r="D351" s="6" t="n">
-        <v>0.04</v>
+      <c r="D351" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E351" s="4" t="inlineStr">
         <is>
@@ -8679,8 +9379,10 @@
           <t>Android Appium Session Management Spec #11</t>
         </is>
       </c>
-      <c r="D352" s="6" t="n">
-        <v>0.06</v>
+      <c r="D352" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E352" s="4" t="inlineStr">
         <is>
@@ -8702,8 +9404,10 @@
           <t>Android Appium Session Management Spec #12</t>
         </is>
       </c>
-      <c r="D353" s="6" t="n">
-        <v>0.08</v>
+      <c r="D353" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E353" s="4" t="inlineStr">
         <is>
@@ -8725,8 +9429,10 @@
           <t>Android Appium Session Management Spec #13</t>
         </is>
       </c>
-      <c r="D354" s="6" t="n">
-        <v>0.1</v>
+      <c r="D354" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E354" s="4" t="inlineStr">
         <is>
@@ -8748,8 +9454,10 @@
           <t>Android Appium Session Management Spec #14</t>
         </is>
       </c>
-      <c r="D355" s="6" t="n">
-        <v>0.12</v>
+      <c r="D355" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E355" s="4" t="inlineStr">
         <is>
@@ -8771,8 +9479,10 @@
           <t>Android Appium Session Management Spec #15</t>
         </is>
       </c>
-      <c r="D356" s="6" t="n">
-        <v>0.04</v>
+      <c r="D356" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E356" s="4" t="inlineStr">
         <is>
@@ -8794,8 +9504,10 @@
           <t>Android Appium Session Management Spec #16</t>
         </is>
       </c>
-      <c r="D357" s="6" t="n">
-        <v>0.06</v>
+      <c r="D357" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E357" s="4" t="inlineStr">
         <is>
@@ -8817,8 +9529,10 @@
           <t>Android Appium Session Management Spec #17</t>
         </is>
       </c>
-      <c r="D358" s="6" t="n">
-        <v>0.08</v>
+      <c r="D358" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E358" s="4" t="inlineStr">
         <is>
@@ -8840,8 +9554,10 @@
           <t>Android Appium Session Management Spec #18</t>
         </is>
       </c>
-      <c r="D359" s="6" t="n">
-        <v>0.1</v>
+      <c r="D359" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E359" s="4" t="inlineStr">
         <is>
@@ -8863,8 +9579,10 @@
           <t>Android Appium Session Management Spec #19</t>
         </is>
       </c>
-      <c r="D360" s="6" t="n">
-        <v>0.12</v>
+      <c r="D360" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E360" s="4" t="inlineStr">
         <is>
@@ -8886,8 +9604,10 @@
           <t>Android Appium Session Management Spec #20</t>
         </is>
       </c>
-      <c r="D361" s="6" t="n">
-        <v>0.04</v>
+      <c r="D361" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E361" s="4" t="inlineStr">
         <is>
@@ -8909,8 +9629,10 @@
           <t>Android Appium Notifications Spec #01</t>
         </is>
       </c>
-      <c r="D362" s="6" t="n">
-        <v>0.06</v>
+      <c r="D362" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E362" s="4" t="inlineStr">
         <is>
@@ -8932,8 +9654,10 @@
           <t>Android Appium Notifications Spec #02</t>
         </is>
       </c>
-      <c r="D363" s="6" t="n">
-        <v>0.08</v>
+      <c r="D363" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E363" s="4" t="inlineStr">
         <is>
@@ -8955,8 +9679,10 @@
           <t>Android Appium Notifications Spec #03</t>
         </is>
       </c>
-      <c r="D364" s="6" t="n">
-        <v>0.1</v>
+      <c r="D364" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E364" s="4" t="inlineStr">
         <is>
@@ -8978,8 +9704,10 @@
           <t>Android Appium Notifications Spec #04</t>
         </is>
       </c>
-      <c r="D365" s="6" t="n">
-        <v>0.12</v>
+      <c r="D365" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E365" s="4" t="inlineStr">
         <is>
@@ -9001,8 +9729,10 @@
           <t>Android Appium Notifications Spec #05</t>
         </is>
       </c>
-      <c r="D366" s="6" t="n">
-        <v>0.04</v>
+      <c r="D366" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E366" s="4" t="inlineStr">
         <is>
@@ -9024,8 +9754,10 @@
           <t>Android Appium Notifications Spec #06</t>
         </is>
       </c>
-      <c r="D367" s="6" t="n">
-        <v>0.06</v>
+      <c r="D367" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E367" s="4" t="inlineStr">
         <is>
@@ -9047,8 +9779,10 @@
           <t>Android Appium Notifications Spec #07</t>
         </is>
       </c>
-      <c r="D368" s="6" t="n">
-        <v>0.08</v>
+      <c r="D368" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E368" s="4" t="inlineStr">
         <is>
@@ -9070,8 +9804,10 @@
           <t>Android Appium Notifications Spec #08</t>
         </is>
       </c>
-      <c r="D369" s="6" t="n">
-        <v>0.1</v>
+      <c r="D369" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E369" s="4" t="inlineStr">
         <is>
@@ -9093,8 +9829,10 @@
           <t>Android Appium Notifications Spec #09</t>
         </is>
       </c>
-      <c r="D370" s="6" t="n">
-        <v>0.12</v>
+      <c r="D370" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E370" s="4" t="inlineStr">
         <is>
@@ -9116,8 +9854,10 @@
           <t>Android Appium Notifications Spec #10</t>
         </is>
       </c>
-      <c r="D371" s="6" t="n">
-        <v>0.04</v>
+      <c r="D371" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E371" s="4" t="inlineStr">
         <is>
@@ -9139,8 +9879,10 @@
           <t>Android Appium File Upload Spec #01</t>
         </is>
       </c>
-      <c r="D372" s="6" t="n">
-        <v>0.06</v>
+      <c r="D372" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E372" s="4" t="inlineStr">
         <is>
@@ -9162,8 +9904,10 @@
           <t>Android Appium File Upload Spec #02</t>
         </is>
       </c>
-      <c r="D373" s="6" t="n">
-        <v>0.08</v>
+      <c r="D373" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E373" s="4" t="inlineStr">
         <is>
@@ -9185,8 +9929,10 @@
           <t>Android Appium File Upload Spec #03</t>
         </is>
       </c>
-      <c r="D374" s="6" t="n">
-        <v>0.1</v>
+      <c r="D374" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E374" s="4" t="inlineStr">
         <is>
@@ -9208,8 +9954,10 @@
           <t>Android Appium File Upload Spec #04</t>
         </is>
       </c>
-      <c r="D375" s="6" t="n">
-        <v>0.12</v>
+      <c r="D375" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E375" s="4" t="inlineStr">
         <is>
@@ -9231,8 +9979,10 @@
           <t>Android Appium File Upload Spec #05</t>
         </is>
       </c>
-      <c r="D376" s="6" t="n">
-        <v>0.04</v>
+      <c r="D376" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E376" s="4" t="inlineStr">
         <is>
@@ -9254,8 +10004,10 @@
           <t>Android Appium File Upload Spec #06</t>
         </is>
       </c>
-      <c r="D377" s="6" t="n">
-        <v>0.06</v>
+      <c r="D377" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E377" s="4" t="inlineStr">
         <is>
@@ -9277,8 +10029,10 @@
           <t>Android Appium File Upload Spec #07</t>
         </is>
       </c>
-      <c r="D378" s="6" t="n">
-        <v>0.08</v>
+      <c r="D378" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E378" s="4" t="inlineStr">
         <is>
@@ -9300,8 +10054,10 @@
           <t>Android Appium File Upload Spec #08</t>
         </is>
       </c>
-      <c r="D379" s="6" t="n">
-        <v>0.1</v>
+      <c r="D379" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E379" s="4" t="inlineStr">
         <is>
@@ -9323,8 +10079,10 @@
           <t>Android Appium File Upload Spec #09</t>
         </is>
       </c>
-      <c r="D380" s="6" t="n">
-        <v>0.12</v>
+      <c r="D380" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E380" s="4" t="inlineStr">
         <is>
@@ -9346,8 +10104,10 @@
           <t>Android Appium File Upload Spec #10</t>
         </is>
       </c>
-      <c r="D381" s="6" t="n">
-        <v>0.04</v>
+      <c r="D381" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E381" s="4" t="inlineStr">
         <is>
@@ -9369,8 +10129,10 @@
           <t>Android Appium Offline Handling Spec #01</t>
         </is>
       </c>
-      <c r="D382" s="6" t="n">
-        <v>0.06</v>
+      <c r="D382" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E382" s="4" t="inlineStr">
         <is>
@@ -9392,8 +10154,10 @@
           <t>Android Appium Offline Handling Spec #02</t>
         </is>
       </c>
-      <c r="D383" s="6" t="n">
-        <v>0.08</v>
+      <c r="D383" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E383" s="4" t="inlineStr">
         <is>
@@ -9415,8 +10179,10 @@
           <t>Android Appium Offline Handling Spec #03</t>
         </is>
       </c>
-      <c r="D384" s="6" t="n">
-        <v>0.1</v>
+      <c r="D384" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E384" s="4" t="inlineStr">
         <is>
@@ -9438,8 +10204,10 @@
           <t>Android Appium Offline Handling Spec #04</t>
         </is>
       </c>
-      <c r="D385" s="6" t="n">
-        <v>0.12</v>
+      <c r="D385" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E385" s="4" t="inlineStr">
         <is>
@@ -9461,8 +10229,10 @@
           <t>Android Appium Accessibility Spec #01</t>
         </is>
       </c>
-      <c r="D386" s="6" t="n">
-        <v>0.04</v>
+      <c r="D386" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E386" s="4" t="inlineStr">
         <is>
@@ -9484,8 +10254,10 @@
           <t>Android Appium Accessibility Spec #02</t>
         </is>
       </c>
-      <c r="D387" s="6" t="n">
-        <v>0.06</v>
+      <c r="D387" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E387" s="4" t="inlineStr">
         <is>
@@ -9507,8 +10279,10 @@
           <t>Android Appium Responsive UI Spec #01</t>
         </is>
       </c>
-      <c r="D388" s="6" t="n">
-        <v>0.08</v>
+      <c r="D388" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E388" s="4" t="inlineStr">
         <is>
@@ -9530,8 +10304,10 @@
           <t>Android Appium Responsive UI Spec #02</t>
         </is>
       </c>
-      <c r="D389" s="6" t="n">
-        <v>0.1</v>
+      <c r="D389" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E389" s="4" t="inlineStr">
         <is>
@@ -9553,8 +10329,10 @@
           <t>Android Appium Responsive UI Spec #03</t>
         </is>
       </c>
-      <c r="D390" s="6" t="n">
-        <v>0.12</v>
+      <c r="D390" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E390" s="4" t="inlineStr">
         <is>
@@ -9576,8 +10354,10 @@
           <t>Android Appium Responsive UI Spec #04</t>
         </is>
       </c>
-      <c r="D391" s="6" t="n">
-        <v>0.04</v>
+      <c r="D391" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E391" s="4" t="inlineStr">
         <is>
@@ -9599,8 +10379,10 @@
           <t>Android Appium Responsive UI Spec #05</t>
         </is>
       </c>
-      <c r="D392" s="6" t="n">
-        <v>0.06</v>
+      <c r="D392" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E392" s="4" t="inlineStr">
         <is>
@@ -9622,8 +10404,10 @@
           <t>Android Appium Responsive UI Spec #06</t>
         </is>
       </c>
-      <c r="D393" s="6" t="n">
-        <v>0.08</v>
+      <c r="D393" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E393" s="4" t="inlineStr">
         <is>
@@ -9645,8 +10429,10 @@
           <t>Android Appium Responsive UI Spec #07</t>
         </is>
       </c>
-      <c r="D394" s="6" t="n">
-        <v>0.1</v>
+      <c r="D394" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E394" s="4" t="inlineStr">
         <is>
@@ -9668,8 +10454,10 @@
           <t>Android Appium Responsive UI Spec #08</t>
         </is>
       </c>
-      <c r="D395" s="6" t="n">
-        <v>0.12</v>
+      <c r="D395" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E395" s="4" t="inlineStr">
         <is>
@@ -9691,8 +10479,10 @@
           <t>Android Appium Responsive UI Spec #09</t>
         </is>
       </c>
-      <c r="D396" s="6" t="n">
-        <v>0.04</v>
+      <c r="D396" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E396" s="4" t="inlineStr">
         <is>
@@ -9714,8 +10504,10 @@
           <t>Android Appium Responsive UI Spec #10</t>
         </is>
       </c>
-      <c r="D397" s="6" t="n">
-        <v>0.06</v>
+      <c r="D397" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E397" s="4" t="inlineStr">
         <is>
@@ -9737,8 +10529,10 @@
           <t>Android Appium Responsive UI Spec #11</t>
         </is>
       </c>
-      <c r="D398" s="6" t="n">
-        <v>0.08</v>
+      <c r="D398" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E398" s="4" t="inlineStr">
         <is>
@@ -9760,8 +10554,10 @@
           <t>Android Appium Performance Smoke Tests Spec #01</t>
         </is>
       </c>
-      <c r="D399" s="6" t="n">
-        <v>0.1</v>
+      <c r="D399" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E399" s="4" t="inlineStr">
         <is>
@@ -9783,8 +10579,10 @@
           <t>Android Appium Regression Suite Spec #01</t>
         </is>
       </c>
-      <c r="D400" s="6" t="n">
-        <v>0.12</v>
+      <c r="D400" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E400" s="4" t="inlineStr">
         <is>
@@ -9806,8 +10604,10 @@
           <t>Android Appium Regression Suite Spec #02</t>
         </is>
       </c>
-      <c r="D401" s="6" t="n">
-        <v>0.04</v>
+      <c r="D401" s="6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
       </c>
       <c r="E401" s="4" t="inlineStr">
         <is>
